--- a/data/output/evaluasi_51.xlsx
+++ b/data/output/evaluasi_51.xlsx
@@ -8,7 +8,15 @@
   </bookViews>
   <sheets>
     <sheet name="5100" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="5171" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="5102" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="5104" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="5103" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5106" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="5107" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5171" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="5101" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="5105" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="5108" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,6 +434,416 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>provinsi</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>6.746467287315569</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>adhb_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHB antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>51</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.568817520595749</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>adhk_net_ekspor_q3-25</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Diskrepansi ADHK antara Provinsi dan total Kabupaten/Kota lebih dari (+-5%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2.29829579613072</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25 vs q-to-q_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>51</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>30.98048987865873</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q2-25 vs q-to-q_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>5.508013232334523</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25 vs q-to-q_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>51</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>5.897602167047079</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q3-25 vs y-on-y_pdrb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,01 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>51</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.37517627845074</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q2-25 vs y-on-y_pklnprt_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>51</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.416281505986531</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q3-25 vs y-on-y_pklnprt_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>51</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-10.64064462500661</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q2-25 vs y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>51</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3.536198841370844</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25 vs y-on-y_pkp_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>51</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>6.871104381103954</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q3-25 vs y-on-y_pmtb_q3-25.1</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>51</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-1.769270480143363</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>51</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Bali</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q2-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>2.980804285101855</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q2-25 vs implisit_y-on-y_pkp_q2-25.1</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -437,7 +855,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>provinsi</t>
+          <t>kabupaten/kota</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -463,29 +881,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>51</v>
+        <v>5108</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Kabupaten Buleleng</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q2-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>-2.088895465975684</v>
+        <v>-5.914000378309106</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>c-to-c_pkp_q2-25 vs c-to-c_pkp_q2-25.1</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Growth lebih dari +- 2 kalinya</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -500,6 +918,916 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5102</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabanan</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-0.8144241888739452</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q3-25_prov vs q-to-q_pdrb_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5102</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabanan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.53273140961169</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5102</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tabanan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-10.33910049574843</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Gianyar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0.692235610834703</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q3-25_prov vs q-to-q_pklnprt_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Gianyar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-16.18578301261395</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Gianyar</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-9.132684609100981</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Gianyar</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-3.271100268516754</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5104</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Gianyar</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2372674151925201</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q3-25_prov vs implisit_y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5103</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Badung</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>13.1463308036965</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5103</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Badung</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>8.304179749753096</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5103</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Badung</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>12.54999833962705</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5106</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangli</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-5.059210490096494</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5106</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangli</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>13.98149888709134</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5106</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Bangli</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.789231182476255</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5107</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Karangasem</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>29.29345035471175</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5107</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Karangasem</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>9.073918357901642</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5107</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Karangasem</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.620059667453204</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5171</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>7.908042484301332</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q3-25_prov vs q-to-q_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5171</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kota Denpasar</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>7.858054941573581</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>5101</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Jembrana</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-9.537327500602018</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q3-25_prov vs y-on-y_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>5101</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Jembrana</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q3-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-7.653035238635572</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -537,29 +1865,29 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>5171</v>
+        <v>5105</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kota Denpasar</t>
+          <t>Kabupaten Klungkung</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>q1-25</t>
+          <t>q3-25</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>40837.52846625447</v>
+        <v>-3.72130968337207</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>adhk_net_ekspor_q1-25_ril vs adhk_net_ekspor_q1-25_rev</t>
+          <t>c-to-c_pkp_q3-25_prov vs c-to-c_pkp_q3-25_kabkot</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Angka revisi lebih dari +- 10 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>

--- a/data/output/evaluasi_51.xlsx
+++ b/data/output/evaluasi_51.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -605,7 +605,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Q-to-Q antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,05 point)</t>
+          <t>Diskrepansi growth Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
         </is>
       </c>
     </row>
@@ -801,7 +801,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi growth C-to-C antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-0,5 point)</t>
+          <t>Diskrepansi Implisit Y-on-Y antara Provinsi dan total Kabupaten/Kota lebih dari (+-1 point)</t>
         </is>
       </c>
     </row>
